--- a/static/files/统一导入模板.xlsx
+++ b/static/files/统一导入模板.xlsx
@@ -1,251 +1,195 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="产品管理" sheetId="1" r:id="rId1"/>
-    <sheet name="订单管理" sheetId="2" r:id="rId2"/>
-    <sheet name="备货管理" sheetId="3" r:id="rId3"/>
-    <sheet name="出货管理" sheetId="4" r:id="rId4"/>
+    <sheet name="产品管理" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="订单管理" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="备货管理" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="出货管理" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="11">
-  <si>
-    <t>客户名称</t>
-  </si>
-  <si>
-    <t>产品名称</t>
-  </si>
-  <si>
-    <t>MINISO国际</t>
-  </si>
-  <si>
-    <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(粉色)</t>
-  </si>
-  <si>
-    <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(棕色)</t>
-  </si>
-  <si>
-    <t>订单数量</t>
-  </si>
-  <si>
-    <t>抵扣备货</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>备货数量</t>
-  </si>
-  <si>
-    <t>出货数量</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="22">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color indexed="8"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -567,166 +511,166 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -791,11 +735,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1082,240 +1089,316 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="Sheet1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="21.625" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
+    <col width="21.625" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:2">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>69码</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>产品价格</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:2">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>MINISO国际</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(粉色)</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:2">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>4</v>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>MINISO国际</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(棕色)</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B$1:B$1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="Sheet2">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="56.875" customWidth="1"/>
-    <col min="3" max="3" width="9.125" customWidth="1"/>
-    <col min="4" max="4" width="8.625" customWidth="1"/>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col width="11.25" customWidth="1" min="1" max="1"/>
+    <col width="56.875" customWidth="1" min="2" max="2"/>
+    <col width="9.125" customWidth="1" min="3" max="3"/>
+    <col width="8.625" customWidth="1" min="4" max="4"/>
+    <col width="12.875" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" customHeight="1" spans="1:5">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
+    <row r="1" ht="27" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>订单数量</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>抵扣备货</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="27" customHeight="1" spans="1:5">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="4">
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>MINISO国际</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(粉色)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="4" t="n">
         <v>5000</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
     </row>
-    <row r="3" ht="27" customHeight="1" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4">
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>MINISO国际</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(棕色)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="4" t="n">
         <v>5000</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="E3" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="Sheet3">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="56.875" customWidth="1"/>
-    <col min="3" max="3" width="10.75" customWidth="1"/>
-    <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col width="11.25" customWidth="1" min="1" max="1"/>
+    <col width="56.875" customWidth="1" min="2" max="2"/>
+    <col width="10.75" customWidth="1" min="3" max="3"/>
+    <col width="12.875" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1" spans="1:4">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
+    <row r="1" ht="33" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>备货数量</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="33" customHeight="1" spans="1:4">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="4">
+    <row r="2" ht="33" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>MINISO国际</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(粉色)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="4" t="n"/>
     </row>
-    <row r="3" ht="33" customHeight="1" spans="1:4">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4">
+    <row r="3" ht="33" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>MINISO国际</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(棕色)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="4" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B3">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="Sheet4">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="56.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.625" customWidth="1"/>
-    <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col width="11.25" customWidth="1" min="1" max="1"/>
+    <col width="56.875" customWidth="1" style="1" min="2" max="2"/>
+    <col width="8.625" customWidth="1" min="3" max="3"/>
+    <col width="12.875" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1" spans="1:4">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
+    <row r="1" ht="33" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>出货数量</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="33" customHeight="1" spans="1:4">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="4">
+    <row r="2" ht="33" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>MINISO国际</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(粉色)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="4" t="n"/>
     </row>
-    <row r="3" ht="33" customHeight="1" spans="1:4">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4">
+    <row r="3" ht="33" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>MINISO国际</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(棕色)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="D3" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B3">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/static/files/统一导入模板.xlsx
+++ b/static/files/统一导入模板.xlsx
@@ -387,7 +387,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -508,6 +508,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -656,7 +662,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -673,6 +679,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1332,12 +1342,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col width="11.25" customWidth="1" min="1" max="1"/>
-    <col width="56.875" customWidth="1" style="1" min="2" max="2"/>
-    <col width="8.625" customWidth="1" min="3" max="3"/>
+    <col width="7.72" customWidth="1" style="1" min="2" max="2"/>
+    <col width="56.69" customWidth="1" min="3" max="3"/>
     <col width="12.875" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1347,17 +1357,22 @@
           <t>客户名称</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>国家</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>产品名称</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>出货数量</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1369,15 +1384,16 @@
           <t>MINISO国际</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(粉色)</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="D2" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3" ht="33" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -1385,15 +1401,16 @@
           <t>MINISO国际</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(棕色)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="D3" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B3">

--- a/static/files/统一导入模板.xlsx
+++ b/static/files/统一导入模板.xlsx
@@ -1,195 +1,422 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28800" windowHeight="12090"/>
   </bookViews>
   <sheets>
-    <sheet name="产品管理" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="订单管理" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="备货管理" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="出货管理" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="产品管理" sheetId="1" r:id="rId1"/>
+    <sheet name="订单管理" sheetId="2" r:id="rId2"/>
+    <sheet name="备货管理" sheetId="3" r:id="rId3"/>
+    <sheet name="出货管理" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_1C43F73BDF4C488FA8A2C4AF19B347DB" descr="qkxXhk"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1" cstate="hqprint"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4800600" y="844550"/>
+          <a:ext cx="744220" cy="762000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="ID_72B27CC9A06A4306AABB5E28C6037F7D" descr="UcEACH"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2" cstate="hqprint"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4800600" y="171450"/>
+          <a:ext cx="744220" cy="762000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="51">
+  <si>
+    <t>客户名称</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>69码</t>
+  </si>
+  <si>
+    <t>产品价格</t>
+  </si>
+  <si>
+    <t>图片</t>
+  </si>
+  <si>
+    <t>MINISO国际</t>
+  </si>
+  <si>
+    <t>3寸MINI FAMILY蒸包毛绒挂件（GIGI猪）</t>
+  </si>
+  <si>
+    <t>3寸MINI FAMILY蒸包毛绒挂件（墩墩）</t>
+  </si>
+  <si>
+    <t>3寸MINI FAMILY蒸包毛绒挂件（奶牛、MEMO猫、熊猫混3款）</t>
+  </si>
+  <si>
+    <t>MINI FAMILY杯面团子系列毛绒公仔盲盒</t>
+  </si>
+  <si>
+    <t>MINI FAMILY海洋变装系列毛绒挂件（鲨鱼熊猫、章鱼pen混2款）</t>
+  </si>
+  <si>
+    <t>MINI FAMILY趴姿毛绒公仔（MIMIBARA）</t>
+  </si>
+  <si>
+    <t>MINI FAMILY趴姿毛绒公仔（MINI PEN）</t>
+  </si>
+  <si>
+    <t>MINI FAMILY趴姿毛绒公仔（PENDY、PENMAN混2款）</t>
+  </si>
+  <si>
+    <t>MINI FAMILY趴姿毛绒公仔（熊猫、MEMO猫混2款）</t>
+  </si>
+  <si>
+    <t>MINI FAMILY团子系列-4寸盲袋公仔（MIMIBARA、猫猫混3款）</t>
+  </si>
+  <si>
+    <t>MINI FAMILY团子系列-4寸盲袋公仔（企鹅混4款）</t>
+  </si>
+  <si>
+    <t>Mini Family外星系列毛绒公仔（飞碟墩）</t>
+  </si>
+  <si>
+    <t>Mini Family外星系列毛绒公仔（黑天鹅墩）</t>
+  </si>
+  <si>
+    <t>Mini Family外星系列毛绒公仔（火箭墩）</t>
+  </si>
+  <si>
+    <t>Mini Family外星系列毛绒公仔（科学家墩）</t>
+  </si>
+  <si>
+    <t>Mini Family外星系列毛绒公仔（太空帽卡皮巴拉）</t>
+  </si>
+  <si>
+    <t>Mini Family外星系列毛绒公仔（土星墩）</t>
+  </si>
+  <si>
+    <t>Mini Family外星系列毛绒公仔（外星墩）</t>
+  </si>
+  <si>
+    <t>Mini Family外星系列毛绒公仔（宇航员pen）</t>
+  </si>
+  <si>
+    <t>Mini Family外星系列毛绒挂件（外星墩）</t>
+  </si>
+  <si>
+    <t>MINI FAMILY夏日系列（混8款花环毛绒挂件、10款趴姿小公仔，含PDQ）</t>
+  </si>
+  <si>
+    <t>MINI FAMILY蒸包毛绒公仔（包子墩、绿饺子墩混2款）（含蒸笼）</t>
+  </si>
+  <si>
+    <t>MINI FAMILY蒸包毛绒公仔（奶牛、MEMO猫、熊猫混3款）（含蒸笼）</t>
+  </si>
+  <si>
+    <t>草莓甜心&amp;Mini Family联名系列盲盒毛绒挂件</t>
+  </si>
+  <si>
+    <t>草莓甜心&amp;Mini Family联名系列毛绒公仔（CICI）</t>
+  </si>
+  <si>
+    <t>草莓甜心&amp;Mini Family联名系列毛绒公仔（MINI PEN）</t>
+  </si>
+  <si>
+    <t>草莓甜心&amp;Mini Family联名系列毛绒公仔（PENDY）</t>
+  </si>
+  <si>
+    <t>单支毛绒花（百合混2款）</t>
+  </si>
+  <si>
+    <t>单支毛绒花（灯笼花）</t>
+  </si>
+  <si>
+    <t>单支毛绒花（粉球菊、小苍兰混2款）</t>
+  </si>
+  <si>
+    <t>单支毛绒花（红玫瑰）</t>
+  </si>
+  <si>
+    <t>单支毛绒花（康乃馨混2款）</t>
+  </si>
+  <si>
+    <t>单支毛绒花（绿色系混3款）</t>
+  </si>
+  <si>
+    <t>天线宝宝&amp;mini family联名毛绒挂件盲盒</t>
+  </si>
+  <si>
+    <t>订单数量</t>
+  </si>
+  <si>
+    <t>抵扣备货</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(粉色)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(棕色)</t>
+  </si>
+  <si>
+    <t>备货数量</t>
+  </si>
+  <si>
+    <t>国家</t>
+  </si>
+  <si>
+    <t>出货数量</t>
+  </si>
+  <si>
+    <t>6927432142518</t>
+  </si>
+  <si>
+    <t>6927432154009</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="22">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color indexed="8"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -387,7 +614,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -508,181 +735,187 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -745,74 +978,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1099,323 +1269,277 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet1">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col width="21.625" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="21.625" customWidth="1"/>
+    <col min="2" max="2" width="63.5" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="29.875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>69码</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>产品价格</t>
-        </is>
+    <row r="1" ht="22" customHeight="1" spans="1:5">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>MINISO国际</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(粉色)</t>
-        </is>
+    <row r="2" ht="73" customHeight="1" spans="1:5">
+      <c r="A2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="11">
+        <v>9.9</v>
+      </c>
+      <c r="E2" s="9" t="str">
+        <f>_xlfn.DISPIMG("ID_72B27CC9A06A4306AABB5E28C6037F7D",1)</f>
+        <v>=DISPIMG("ID_72B27CC9A06A4306AABB5E28C6037F7D",1)</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>MINISO国际</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(棕色)</t>
-        </is>
+    <row r="3" ht="73" customHeight="1" spans="1:5">
+      <c r="A3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="11">
+        <v>9.9</v>
+      </c>
+      <c r="E3" s="9" t="str">
+        <f>_xlfn.DISPIMG("ID_1C43F73BDF4C488FA8A2C4AF19B347DB",1)</f>
+        <v>=DISPIMG("ID_1C43F73BDF4C488FA8A2C4AF19B347DB",1)</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
+  <conditionalFormatting sqref="B$1:B$1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet2">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="4"/>
   <cols>
-    <col width="11.25" customWidth="1" min="1" max="1"/>
-    <col width="56.875" customWidth="1" min="2" max="2"/>
-    <col width="9.125" customWidth="1" min="3" max="3"/>
-    <col width="8.625" customWidth="1" min="4" max="4"/>
-    <col width="12.875" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="11.25" customWidth="1"/>
+    <col min="2" max="2" width="56.875" customWidth="1"/>
+    <col min="3" max="3" width="9.125" customWidth="1"/>
+    <col min="4" max="4" width="8.625" customWidth="1"/>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>订单数量</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>抵扣备货</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
+    <row r="1" ht="27" customHeight="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="2" ht="27" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>MINISO国际</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(粉色)</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
+    <row r="2" ht="27" customHeight="1" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="4">
         <v>10000</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="4">
         <v>5000</v>
       </c>
-      <c r="E2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>MINISO国际</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(棕色)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
+    <row r="3" ht="27" customHeight="1" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="4">
         <v>10000</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="4">
         <v>5000</v>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3">
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet3">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
-    <col width="11.25" customWidth="1" min="1" max="1"/>
-    <col width="56.875" customWidth="1" min="2" max="2"/>
-    <col width="10.75" customWidth="1" min="3" max="3"/>
-    <col width="12.875" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="11.25" customWidth="1"/>
+    <col min="2" max="2" width="56.875" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>备货数量</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
+    <row r="1" ht="33" customHeight="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="2" ht="33" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>MINISO国际</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(粉色)</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
+    <row r="2" ht="33" customHeight="1" spans="1:4">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="4">
         <v>10000</v>
       </c>
-      <c r="D2" s="4" t="n"/>
+      <c r="D2" s="4"/>
     </row>
-    <row r="3" ht="33" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>MINISO国际</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(棕色)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
+    <row r="3" ht="33" customHeight="1" spans="1:4">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="4">
         <v>10000</v>
       </c>
-      <c r="D3" s="4" t="n"/>
+      <c r="D3" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B3">
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet4">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="4"/>
   <cols>
-    <col width="11.25" customWidth="1" min="1" max="1"/>
-    <col width="7.72" customWidth="1" style="1" min="2" max="2"/>
-    <col width="56.69" customWidth="1" min="3" max="3"/>
-    <col width="12.875" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="11.25" customWidth="1"/>
+    <col min="2" max="2" width="7.71666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="56.6916666666667" customWidth="1"/>
+    <col min="4" max="4" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>国家</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>出货数量</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
+    <row r="1" ht="33" customHeight="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="2" ht="33" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>MINISO国际</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(粉色)</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
+    <row r="2" ht="33" customHeight="1" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="4">
         <v>10000</v>
       </c>
-      <c r="E2" s="4" t="n"/>
+      <c r="E2" s="4"/>
     </row>
-    <row r="3" ht="33" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>MINISO国际</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(棕色)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
+    <row r="3" ht="33" customHeight="1" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="4">
         <v>10000</v>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B3">
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/static/files/统一导入模板.xlsx
+++ b/static/files/统一导入模板.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="28800" windowHeight="12090"/>
   </bookViews>
   <sheets>
-    <sheet name="产品管理" sheetId="1" r:id="rId1"/>
+    <sheet name="新品录入" sheetId="1" r:id="rId1"/>
     <sheet name="订单管理" sheetId="2" r:id="rId2"/>
     <sheet name="备货管理" sheetId="3" r:id="rId3"/>
     <sheet name="出货管理" sheetId="4" r:id="rId4"/>
@@ -34,46 +34,58 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="ID_1C43F73BDF4C488FA8A2C4AF19B347DB" descr="qkxXhk"/>
-        <xdr:cNvPicPr/>
+        <xdr:cNvPr id="3" name="ID_B3509D531F63482A9A320652FCAB53C5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1" cstate="hqprint"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4800600" y="844550"/>
-          <a:ext cx="744220" cy="762000"/>
+          <a:off x="9314180" y="736600"/>
+          <a:ext cx="1013460" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="ID_72B27CC9A06A4306AABB5E28C6037F7D" descr="UcEACH"/>
-        <xdr:cNvPicPr/>
+        <xdr:cNvPr id="4" name="ID_25C3C7E5D82C444C9F3D8C57B30E45A3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2" cstate="hqprint"/>
+        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4800600" y="171450"/>
-          <a:ext cx="744220" cy="762000"/>
+          <a:off x="9477375" y="2802890"/>
+          <a:ext cx="1222375" cy="2032635"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
@@ -81,128 +93,95 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="39">
+  <si>
+    <t>客户</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>工厂</t>
+  </si>
+  <si>
+    <t>69码</t>
+  </si>
+  <si>
+    <t>产品价格</t>
+  </si>
+  <si>
+    <t>图片</t>
+  </si>
+  <si>
+    <t>MINISO国际</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-M(花猫)</t>
+  </si>
+  <si>
+    <t>东莞</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-XL(卡皮巴拉)</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-XXL(卡皮巴拉)</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-S-KJ(美西螈)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+16.5</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-M-KJ(美西螈)</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-L-KJ(美西螈)</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-XL-KJ(美西螈)</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-XXL-KJ(美西螈)</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-S-KJ(橘猫)</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-M-KJ(橘猫)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+MINISO长条靠枕-XXL-KJ(橘猫)</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-S-KJ(黑粉猫)</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-M-KJ(黑粉猫)</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-L-KJ(黑粉猫)</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-XL-KJ(黑粉猫)</t>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-XXL-KJ(黑粉猫)</t>
+  </si>
+  <si>
+    <t>Sanrio Characters系列奶嘴毛绒挂件(混)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+Sanrio Characters系列头型毛绒挂件(混)</t>
+  </si>
   <si>
     <t>客户名称</t>
   </si>
   <si>
-    <t>产品名称</t>
-  </si>
-  <si>
-    <t>69码</t>
-  </si>
-  <si>
-    <t>产品价格</t>
-  </si>
-  <si>
-    <t>图片</t>
-  </si>
-  <si>
-    <t>MINISO国际</t>
-  </si>
-  <si>
-    <t>3寸MINI FAMILY蒸包毛绒挂件（GIGI猪）</t>
-  </si>
-  <si>
-    <t>3寸MINI FAMILY蒸包毛绒挂件（墩墩）</t>
-  </si>
-  <si>
-    <t>3寸MINI FAMILY蒸包毛绒挂件（奶牛、MEMO猫、熊猫混3款）</t>
-  </si>
-  <si>
-    <t>MINI FAMILY杯面团子系列毛绒公仔盲盒</t>
-  </si>
-  <si>
-    <t>MINI FAMILY海洋变装系列毛绒挂件（鲨鱼熊猫、章鱼pen混2款）</t>
-  </si>
-  <si>
-    <t>MINI FAMILY趴姿毛绒公仔（MIMIBARA）</t>
-  </si>
-  <si>
-    <t>MINI FAMILY趴姿毛绒公仔（MINI PEN）</t>
-  </si>
-  <si>
-    <t>MINI FAMILY趴姿毛绒公仔（PENDY、PENMAN混2款）</t>
-  </si>
-  <si>
-    <t>MINI FAMILY趴姿毛绒公仔（熊猫、MEMO猫混2款）</t>
-  </si>
-  <si>
-    <t>MINI FAMILY团子系列-4寸盲袋公仔（MIMIBARA、猫猫混3款）</t>
-  </si>
-  <si>
-    <t>MINI FAMILY团子系列-4寸盲袋公仔（企鹅混4款）</t>
-  </si>
-  <si>
-    <t>Mini Family外星系列毛绒公仔（飞碟墩）</t>
-  </si>
-  <si>
-    <t>Mini Family外星系列毛绒公仔（黑天鹅墩）</t>
-  </si>
-  <si>
-    <t>Mini Family外星系列毛绒公仔（火箭墩）</t>
-  </si>
-  <si>
-    <t>Mini Family外星系列毛绒公仔（科学家墩）</t>
-  </si>
-  <si>
-    <t>Mini Family外星系列毛绒公仔（太空帽卡皮巴拉）</t>
-  </si>
-  <si>
-    <t>Mini Family外星系列毛绒公仔（土星墩）</t>
-  </si>
-  <si>
-    <t>Mini Family外星系列毛绒公仔（外星墩）</t>
-  </si>
-  <si>
-    <t>Mini Family外星系列毛绒公仔（宇航员pen）</t>
-  </si>
-  <si>
-    <t>Mini Family外星系列毛绒挂件（外星墩）</t>
-  </si>
-  <si>
-    <t>MINI FAMILY夏日系列（混8款花环毛绒挂件、10款趴姿小公仔，含PDQ）</t>
-  </si>
-  <si>
-    <t>MINI FAMILY蒸包毛绒公仔（包子墩、绿饺子墩混2款）（含蒸笼）</t>
-  </si>
-  <si>
-    <t>MINI FAMILY蒸包毛绒公仔（奶牛、MEMO猫、熊猫混3款）（含蒸笼）</t>
-  </si>
-  <si>
-    <t>草莓甜心&amp;Mini Family联名系列盲盒毛绒挂件</t>
-  </si>
-  <si>
-    <t>草莓甜心&amp;Mini Family联名系列毛绒公仔（CICI）</t>
-  </si>
-  <si>
-    <t>草莓甜心&amp;Mini Family联名系列毛绒公仔（MINI PEN）</t>
-  </si>
-  <si>
-    <t>草莓甜心&amp;Mini Family联名系列毛绒公仔（PENDY）</t>
-  </si>
-  <si>
-    <t>单支毛绒花（百合混2款）</t>
-  </si>
-  <si>
-    <t>单支毛绒花（灯笼花）</t>
-  </si>
-  <si>
-    <t>单支毛绒花（粉球菊、小苍兰混2款）</t>
-  </si>
-  <si>
-    <t>单支毛绒花（红玫瑰）</t>
-  </si>
-  <si>
-    <t>单支毛绒花（康乃馨混2款）</t>
-  </si>
-  <si>
-    <t>单支毛绒花（绿色系混3款）</t>
-  </si>
-  <si>
-    <t>天线宝宝&amp;mini family联名毛绒挂件盲盒</t>
-  </si>
-  <si>
     <t>订单数量</t>
   </si>
   <si>
@@ -212,28 +191,28 @@
     <t>备注</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>MINISO长条靠枕-XXL-KJ(橘猫)</t>
+  </si>
+  <si>
+    <t>Sanrio Characters系列头型毛绒挂件(混)</t>
+  </si>
+  <si>
+    <t>国家</t>
+  </si>
+  <si>
+    <t>出货数量</t>
+  </si>
+  <si>
     <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(粉色)</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>墩墩疯狂假期系列-猫头鹰墩毛绒公仔(棕色)</t>
   </si>
   <si>
     <t>备货数量</t>
-  </si>
-  <si>
-    <t>国家</t>
-  </si>
-  <si>
-    <t>出货数量</t>
-  </si>
-  <si>
-    <t>6927432142518</t>
-  </si>
-  <si>
-    <t>6927432154009</t>
   </si>
 </sst>
 </file>
@@ -246,7 +225,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,6 +247,16 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -753,137 +742,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -901,19 +890,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1271,71 +1263,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.625" customWidth="1"/>
     <col min="2" max="2" width="63.5" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="29.875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="20.35" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="29.875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:5">
-      <c r="A1" s="8" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:6">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="11" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" ht="73" customHeight="1" spans="1:5">
-      <c r="A2" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="9" t="s">
+    <row r="2" ht="121" customHeight="1" spans="1:6">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="B2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="12">
+        <v>25</v>
+      </c>
+      <c r="F2" s="11" t="str">
+        <f>_xlfn.DISPIMG("ID_B3509D531F63482A9A320652FCAB53C5",1)</f>
+        <v>=DISPIMG("ID_B3509D531F63482A9A320652FCAB53C5",1)</v>
+      </c>
+    </row>
+    <row r="3" ht="121" customHeight="1" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="12">
         <v>49</v>
       </c>
-      <c r="D2" s="11">
-        <v>9.9</v>
-      </c>
-      <c r="E2" s="9" t="str">
-        <f>_xlfn.DISPIMG("ID_72B27CC9A06A4306AABB5E28C6037F7D",1)</f>
-        <v>=DISPIMG("ID_72B27CC9A06A4306AABB5E28C6037F7D",1)</v>
-      </c>
-    </row>
-    <row r="3" ht="73" customHeight="1" spans="1:5">
-      <c r="A3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="11">
-        <v>9.9</v>
-      </c>
-      <c r="E3" s="9" t="str">
-        <f>_xlfn.DISPIMG("ID_1C43F73BDF4C488FA8A2C4AF19B347DB",1)</f>
-        <v>=DISPIMG("ID_1C43F73BDF4C488FA8A2C4AF19B347DB",1)</v>
+      <c r="F3" s="11" t="str">
+        <f>_xlfn.DISPIMG("ID_25C3C7E5D82C444C9F3D8C57B30E45A3",1)</f>
+        <v>=DISPIMG("ID_25C3C7E5D82C444C9F3D8C57B30E45A3",1)</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B$1:B$1048576">
+  <conditionalFormatting sqref="B$1:C$1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1347,7 +1345,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="11.25" customWidth="1"/>
     <col min="2" max="2" width="56.875" customWidth="1"/>
@@ -1358,53 +1356,49 @@
   <sheetData>
     <row r="1" ht="27" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" ht="27" customHeight="1" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="4">
-        <v>10000</v>
-      </c>
-      <c r="D2" s="4">
-        <v>5000</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8">
+        <v>40</v>
+      </c>
+      <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" ht="27" customHeight="1" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="4">
-        <v>10000</v>
-      </c>
-      <c r="D3" s="4">
-        <v>5000</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="8">
+        <v>20</v>
+      </c>
+      <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1423,54 +1417,57 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="56.875" customWidth="1"/>
+    <col min="2" max="2" width="56.875" style="7" customWidth="1"/>
     <col min="3" max="3" width="10.75" customWidth="1"/>
     <col min="4" max="4" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" ht="33" customHeight="1" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="4">
-        <v>10000</v>
+        <v>6</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8">
+        <v>40</v>
       </c>
       <c r="D2" s="4"/>
     </row>
     <row r="3" ht="33" customHeight="1" spans="1:4">
       <c r="A3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="4">
-        <v>10000</v>
+        <v>6</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="8">
+        <v>20</v>
       </c>
       <c r="D3" s="4"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1492,28 +1489,28 @@
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" ht="33" customHeight="1" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D2" s="4">
         <v>10000</v>
@@ -1522,17 +1519,17 @@
     </row>
     <row r="3" ht="33" customHeight="1" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D3" s="4">
         <v>10000</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
